--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/suggestCalcData.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/suggestCalcData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="1 - 历史销量 &amp; 去噪销量" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,13 +494,6 @@
     <font>
       <sz val="9.75"/>
       <color rgb="FFF54A45"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1065,133 +1058,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1205,13 +1198,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1220,7 +1213,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1772,7 +1765,7 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/mrp/suggestCalcData.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/mrp/suggestCalcData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="1 - 历史销量 &amp; 去噪销量" sheetId="1" r:id="rId1"/>
@@ -463,7 +463,7 @@
     <t>固定值去噪</t>
   </si>
   <si>
-    <t>{.percentageEffectiveValue}</t>
+    <t>{.percentageValue}</t>
   </si>
 </sst>
 </file>
@@ -2370,6 +2370,10 @@
   <sheetPr/>
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="5" max="5" width="23.625" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
@@ -2408,7 +2412,7 @@
         <v>103</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
